--- a/Results_experiment/exp_4/preds_1111112222222222.xlsx
+++ b/Results_experiment/exp_4/preds_1111112222222222.xlsx
@@ -1596,7 +1596,7 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>1.378294229507446</v>
+        <v>1.739962935447693</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1610,7 +1610,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D3">
-        <v>1.602637529373169</v>
+        <v>2.164747953414917</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1624,7 +1624,7 @@
         <v>21.89999961853027</v>
       </c>
       <c r="D4">
-        <v>15.91436958312988</v>
+        <v>14.84710311889648</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1638,7 +1638,7 @@
         <v>25.89999961853027</v>
       </c>
       <c r="D5">
-        <v>14.72086238861084</v>
+        <v>15.25471115112305</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1652,7 +1652,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D6">
-        <v>2.540656328201294</v>
+        <v>3.088241577148438</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1666,7 +1666,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D7">
-        <v>5.253562450408936</v>
+        <v>4.861476898193359</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1680,7 +1680,7 @@
         <v>27.39999961853027</v>
       </c>
       <c r="D8">
-        <v>18.56378173828125</v>
+        <v>20.2763843536377</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1694,7 +1694,7 @@
         <v>20.5</v>
       </c>
       <c r="D9">
-        <v>10.91462421417236</v>
+        <v>11.68049240112305</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1708,7 +1708,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D10">
-        <v>6.269382476806641</v>
+        <v>6.352284908294678</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1722,7 +1722,7 @@
         <v>33.09999847412109</v>
       </c>
       <c r="D11">
-        <v>23.20822143554688</v>
+        <v>23.32969856262207</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1736,7 +1736,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D12">
-        <v>4.616726875305176</v>
+        <v>3.978210926055908</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1750,7 +1750,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D13">
-        <v>2.676071643829346</v>
+        <v>2.327915191650391</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1764,7 +1764,7 @@
         <v>4</v>
       </c>
       <c r="D14">
-        <v>3.028547763824463</v>
+        <v>3.422615528106689</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1778,7 +1778,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D15">
-        <v>3.29695463180542</v>
+        <v>3.361032009124756</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1792,7 +1792,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D16">
-        <v>3.250581502914429</v>
+        <v>4.509950160980225</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1806,7 +1806,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D17">
-        <v>1.565152406692505</v>
+        <v>1.702490448951721</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1820,7 +1820,7 @@
         <v>12</v>
       </c>
       <c r="D18">
-        <v>10.82681941986084</v>
+        <v>11.38915824890137</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1834,7 +1834,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>2.798820018768311</v>
+        <v>2.954718589782715</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1848,7 +1848,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D20">
-        <v>1.389211058616638</v>
+        <v>3.433221340179443</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1862,7 +1862,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D21">
-        <v>4.771563529968262</v>
+        <v>4.35629940032959</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1876,7 +1876,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D22">
-        <v>1.3608717918396</v>
+        <v>1.210835814476013</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1890,7 +1890,7 @@
         <v>13.80000019073486</v>
       </c>
       <c r="D23">
-        <v>11.25885581970215</v>
+        <v>8.977237701416016</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1904,7 +1904,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D24">
-        <v>1.357983112335205</v>
+        <v>1.68378484249115</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1918,7 +1918,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D25">
-        <v>2.478630065917969</v>
+        <v>2.678086042404175</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1932,7 +1932,7 @@
         <v>37.90000152587891</v>
       </c>
       <c r="D26">
-        <v>31.06431770324707</v>
+        <v>30.8843936920166</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1946,7 +1946,7 @@
         <v>5.5</v>
       </c>
       <c r="D27">
-        <v>5.633062362670898</v>
+        <v>4.85075569152832</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1960,7 +1960,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D28">
-        <v>5.503857612609863</v>
+        <v>6.036931037902832</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1974,7 +1974,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D29">
-        <v>2.934544801712036</v>
+        <v>2.760429859161377</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1988,7 +1988,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D30">
-        <v>1.355567455291748</v>
+        <v>1.305794954299927</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2002,7 +2002,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D31">
-        <v>1.825582981109619</v>
+        <v>2.423357009887695</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2016,7 +2016,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D32">
-        <v>1.395327091217041</v>
+        <v>2.129056453704834</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2030,7 +2030,7 @@
         <v>5.5</v>
       </c>
       <c r="D33">
-        <v>5.136417388916016</v>
+        <v>3.677423000335693</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2044,7 +2044,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D34">
-        <v>2.699806451797485</v>
+        <v>2.491550922393799</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2058,7 +2058,7 @@
         <v>4.5</v>
       </c>
       <c r="D35">
-        <v>5.127380847930908</v>
+        <v>5.244152545928955</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2072,7 +2072,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D36">
-        <v>1.909310817718506</v>
+        <v>4.202707290649414</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2086,7 +2086,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D37">
-        <v>2.104103088378906</v>
+        <v>1.796974658966064</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2100,7 +2100,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D38">
-        <v>1.421075820922852</v>
+        <v>1.836894035339355</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2114,7 +2114,7 @@
         <v>0.5</v>
       </c>
       <c r="D39">
-        <v>1.358439922332764</v>
+        <v>1.253113508224487</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2128,7 +2128,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D40">
-        <v>1.9208003282547</v>
+        <v>2.629019260406494</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2142,7 +2142,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D41">
-        <v>1.370440483093262</v>
+        <v>1.768341302871704</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2156,7 +2156,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="D42">
-        <v>5.265703678131104</v>
+        <v>5.575775623321533</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2170,7 +2170,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D43">
-        <v>1.470883011817932</v>
+        <v>1.430867910385132</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2184,7 +2184,7 @@
         <v>5</v>
       </c>
       <c r="D44">
-        <v>4.207212448120117</v>
+        <v>4.333229064941406</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2198,7 +2198,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D45">
-        <v>1.725274801254272</v>
+        <v>1.681875944137573</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2212,7 +2212,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D46">
-        <v>3.791408538818359</v>
+        <v>3.440024852752686</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2226,7 +2226,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D47">
-        <v>2.856385946273804</v>
+        <v>1.880130529403687</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2240,7 +2240,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D48">
-        <v>5.533395767211914</v>
+        <v>4.396088123321533</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2254,7 +2254,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D49">
-        <v>1.625170707702637</v>
+        <v>4.141993045806885</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2268,7 +2268,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D50">
-        <v>5.477492809295654</v>
+        <v>5.329624652862549</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2282,7 +2282,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D51">
-        <v>2.522084951400757</v>
+        <v>2.046625375747681</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2296,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="D52">
-        <v>2.559059143066406</v>
+        <v>2.306644916534424</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2310,7 +2310,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D53">
-        <v>2.192272186279297</v>
+        <v>2.966123819351196</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2324,7 +2324,7 @@
         <v>5.5</v>
       </c>
       <c r="D54">
-        <v>1.377723813056946</v>
+        <v>3.335555076599121</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2338,7 +2338,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D55">
-        <v>1.369295716285706</v>
+        <v>1.31993567943573</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2352,7 +2352,7 @@
         <v>34</v>
       </c>
       <c r="D56">
-        <v>20.65257453918457</v>
+        <v>22.35369682312012</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2366,7 +2366,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D57">
-        <v>3.293428659439087</v>
+        <v>4.119178771972656</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2380,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="D58">
-        <v>1.557348489761353</v>
+        <v>2.13748836517334</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2394,7 +2394,7 @@
         <v>3.5</v>
       </c>
       <c r="D59">
-        <v>2.044336795806885</v>
+        <v>1.983323693275452</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2408,7 +2408,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D60">
-        <v>2.676650762557983</v>
+        <v>2.12578558921814</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2422,7 +2422,7 @@
         <v>6</v>
       </c>
       <c r="D61">
-        <v>1.386757135391235</v>
+        <v>1.985039472579956</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2436,7 +2436,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D62">
-        <v>5.787643909454346</v>
+        <v>5.038629531860352</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2450,7 +2450,7 @@
         <v>8</v>
       </c>
       <c r="D63">
-        <v>8.911539077758789</v>
+        <v>9.878957748413086</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2464,7 +2464,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D64">
-        <v>1.405111908912659</v>
+        <v>2.207940101623535</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2478,7 +2478,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D65">
-        <v>9.076395034790039</v>
+        <v>9.428262710571289</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2492,7 +2492,7 @@
         <v>28.20000076293945</v>
       </c>
       <c r="D66">
-        <v>14.28348827362061</v>
+        <v>15.93670845031738</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2506,7 +2506,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D67">
-        <v>5.202141761779785</v>
+        <v>4.95380973815918</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2520,7 +2520,7 @@
         <v>0.5</v>
       </c>
       <c r="D68">
-        <v>1.405806303024292</v>
+        <v>1.998475790023804</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2534,7 +2534,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D69">
-        <v>9.170427322387695</v>
+        <v>7.240161418914795</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2548,7 +2548,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D70">
-        <v>2.001529216766357</v>
+        <v>2.362548112869263</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2562,7 +2562,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D71">
-        <v>1.351287722587585</v>
+        <v>1.829856634140015</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2576,7 +2576,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D72">
-        <v>4.948508262634277</v>
+        <v>4.664749145507812</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2590,7 +2590,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D73">
-        <v>1.479886293411255</v>
+        <v>1.943004965782166</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2604,7 +2604,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D74">
-        <v>7.062020301818848</v>
+        <v>5.086416244506836</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2618,7 +2618,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D75">
-        <v>5.56445837020874</v>
+        <v>4.259509086608887</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>1.474862813949585</v>
+        <v>1.521171808242798</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2646,7 +2646,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D77">
-        <v>1.772776007652283</v>
+        <v>1.792965173721313</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2660,7 +2660,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D78">
-        <v>4.997699737548828</v>
+        <v>4.974861145019531</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2674,7 +2674,7 @@
         <v>9.5</v>
       </c>
       <c r="D79">
-        <v>3.836867332458496</v>
+        <v>12.84907722473145</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2688,7 +2688,7 @@
         <v>0.5</v>
       </c>
       <c r="D80">
-        <v>2.413620948791504</v>
+        <v>1.866788506507874</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2702,7 +2702,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D81">
-        <v>3.526988983154297</v>
+        <v>3.463133335113525</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2716,7 +2716,7 @@
         <v>1.5</v>
       </c>
       <c r="D82">
-        <v>2.076843500137329</v>
+        <v>2.790259599685669</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2730,7 +2730,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D83">
-        <v>1.441428661346436</v>
+        <v>1.860859155654907</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2744,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>2.990745306015015</v>
+        <v>2.357499122619629</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2758,7 +2758,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D85">
-        <v>2.672530651092529</v>
+        <v>3.244648456573486</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2772,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="D86">
-        <v>1.395808935165405</v>
+        <v>2.12734580039978</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2786,7 +2786,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D87">
-        <v>8.31480598449707</v>
+        <v>9.141105651855469</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2800,7 +2800,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D88">
-        <v>2.405112266540527</v>
+        <v>1.76913595199585</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2814,7 +2814,7 @@
         <v>15</v>
       </c>
       <c r="D89">
-        <v>12.18546295166016</v>
+        <v>11.4534912109375</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2828,7 +2828,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D90">
-        <v>6.225898742675781</v>
+        <v>6.315183639526367</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2842,7 +2842,7 @@
         <v>14</v>
       </c>
       <c r="D91">
-        <v>15.87610054016113</v>
+        <v>17.19180679321289</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2856,7 +2856,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D92">
-        <v>1.364936590194702</v>
+        <v>1.766674995422363</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2870,7 +2870,7 @@
         <v>7.5</v>
       </c>
       <c r="D93">
-        <v>4.833821296691895</v>
+        <v>3.658340454101562</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2884,7 +2884,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D94">
-        <v>1.383363008499146</v>
+        <v>1.559749841690063</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2898,7 +2898,7 @@
         <v>2</v>
       </c>
       <c r="D95">
-        <v>2.977002143859863</v>
+        <v>2.472184658050537</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2912,7 +2912,7 @@
         <v>15.5</v>
       </c>
       <c r="D96">
-        <v>9.355420112609863</v>
+        <v>9.92547607421875</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2926,7 +2926,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D97">
-        <v>2.800886869430542</v>
+        <v>2.236562967300415</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2940,7 +2940,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D98">
-        <v>14.39957809448242</v>
+        <v>8.548395156860352</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2954,7 +2954,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D99">
-        <v>2.316605091094971</v>
+        <v>3.059131145477295</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2968,7 +2968,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D100">
-        <v>2.534677743911743</v>
+        <v>3.148152351379395</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2982,7 +2982,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D101">
-        <v>1.87873649597168</v>
+        <v>2.28993034362793</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2996,7 +2996,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D102">
-        <v>1.409133195877075</v>
+        <v>2.123105049133301</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3010,7 +3010,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D103">
-        <v>4.635586738586426</v>
+        <v>1.829250335693359</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3024,7 +3024,7 @@
         <v>2</v>
       </c>
       <c r="D104">
-        <v>1.726940512657166</v>
+        <v>2.377540588378906</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3038,7 +3038,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D105">
-        <v>5.775328159332275</v>
+        <v>5.924291610717773</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3052,7 +3052,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D106">
-        <v>2.473729372024536</v>
+        <v>2.724230766296387</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3066,7 +3066,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D107">
-        <v>2.19465160369873</v>
+        <v>2.741184234619141</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3080,7 +3080,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D108">
-        <v>5.88913631439209</v>
+        <v>5.14372730255127</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3094,7 +3094,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D109">
-        <v>2.081824779510498</v>
+        <v>2.719422101974487</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3108,7 +3108,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D110">
-        <v>1.373180866241455</v>
+        <v>1.494256734848022</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3122,7 +3122,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D111">
-        <v>2.459068536758423</v>
+        <v>2.759960889816284</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3136,7 +3136,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D112">
-        <v>5.211038112640381</v>
+        <v>6.011486053466797</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3150,7 +3150,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D113">
-        <v>1.970916628837585</v>
+        <v>2.556320667266846</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3164,7 +3164,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D114">
-        <v>6.520135879516602</v>
+        <v>3.899253368377686</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3178,7 +3178,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D115">
-        <v>2.198125123977661</v>
+        <v>1.736072897911072</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3192,7 +3192,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D116">
-        <v>6.237609386444092</v>
+        <v>2.500396966934204</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3206,7 +3206,7 @@
         <v>2</v>
       </c>
       <c r="D117">
-        <v>1.953878164291382</v>
+        <v>3.036975860595703</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3220,7 +3220,7 @@
         <v>2</v>
       </c>
       <c r="D118">
-        <v>1.474312305450439</v>
+        <v>1.875452280044556</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3234,7 +3234,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D119">
-        <v>1.478680610656738</v>
+        <v>2.000417947769165</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3248,7 +3248,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D120">
-        <v>9.508801460266113</v>
+        <v>11.10921669006348</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3262,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="D121">
-        <v>2.540663003921509</v>
+        <v>2.124752521514893</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3276,7 +3276,7 @@
         <v>31.39999961853027</v>
       </c>
       <c r="D122">
-        <v>22.9123363494873</v>
+        <v>20.92444801330566</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3290,7 +3290,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D123">
-        <v>2.819101095199585</v>
+        <v>1.999133586883545</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3304,7 +3304,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D124">
-        <v>1.392806649208069</v>
+        <v>2.46964168548584</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3318,7 +3318,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D125">
-        <v>1.366248846054077</v>
+        <v>3.676960945129395</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3332,7 +3332,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D126">
-        <v>2.369500875473022</v>
+        <v>2.095723390579224</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3346,7 +3346,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D127">
-        <v>4.989717483520508</v>
+        <v>4.708452701568604</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3360,7 +3360,7 @@
         <v>2</v>
       </c>
       <c r="D128">
-        <v>2.485091686248779</v>
+        <v>2.983634471893311</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3374,7 +3374,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D129">
-        <v>2.023196458816528</v>
+        <v>2.565405607223511</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3388,7 +3388,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D130">
-        <v>2.987186193466187</v>
+        <v>2.560140132904053</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3402,7 +3402,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D131">
-        <v>2.712481498718262</v>
+        <v>2.754032611846924</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3416,7 +3416,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D132">
-        <v>3.710284471511841</v>
+        <v>4.421929836273193</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3430,7 +3430,7 @@
         <v>1.5</v>
       </c>
       <c r="D133">
-        <v>2.249718904495239</v>
+        <v>1.861773014068604</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3444,7 +3444,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D134">
-        <v>2.542543649673462</v>
+        <v>3.566087484359741</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3458,7 +3458,7 @@
         <v>3.5</v>
       </c>
       <c r="D135">
-        <v>1.449199199676514</v>
+        <v>2.986774682998657</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3472,7 +3472,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D136">
-        <v>2.881001949310303</v>
+        <v>3.27769136428833</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3486,7 +3486,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D137">
-        <v>6.540693283081055</v>
+        <v>7.796428680419922</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3500,7 +3500,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D138">
-        <v>1.363281011581421</v>
+        <v>1.903919219970703</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3514,7 +3514,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D139">
-        <v>1.370224475860596</v>
+        <v>1.307304501533508</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3528,7 +3528,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D140">
-        <v>3.395143270492554</v>
+        <v>2.998355388641357</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3542,7 +3542,7 @@
         <v>6</v>
       </c>
       <c r="D141">
-        <v>6.31089973449707</v>
+        <v>5.426517486572266</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3556,7 +3556,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D142">
-        <v>1.416545152664185</v>
+        <v>2.043427467346191</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3570,7 +3570,7 @@
         <v>4</v>
       </c>
       <c r="D143">
-        <v>3.578831911087036</v>
+        <v>1.658739686012268</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3584,7 +3584,7 @@
         <v>3</v>
       </c>
       <c r="D144">
-        <v>2.097194910049438</v>
+        <v>1.845049142837524</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3598,7 +3598,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D145">
-        <v>7.307366371154785</v>
+        <v>6.751086711883545</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3612,7 +3612,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D146">
-        <v>1.744598388671875</v>
+        <v>1.891668915748596</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3626,7 +3626,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D147">
-        <v>1.470281600952148</v>
+        <v>1.996978521347046</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3640,7 +3640,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D148">
-        <v>2.893218994140625</v>
+        <v>1.850561141967773</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3654,7 +3654,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D149">
-        <v>5.819889068603516</v>
+        <v>6.761339664459229</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3668,7 +3668,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D150">
-        <v>1.381812214851379</v>
+        <v>1.26151704788208</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3682,7 +3682,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D151">
-        <v>7.121143817901611</v>
+        <v>6.751715660095215</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3696,7 +3696,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D152">
-        <v>1.786246061325073</v>
+        <v>1.965910911560059</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3710,7 +3710,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D153">
-        <v>7.147262573242188</v>
+        <v>7.612013339996338</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3724,7 +3724,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D154">
-        <v>1.356102347373962</v>
+        <v>1.336321115493774</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3738,7 +3738,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D155">
-        <v>1.356070280075073</v>
+        <v>1.286236882209778</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3752,7 +3752,7 @@
         <v>8</v>
       </c>
       <c r="D156">
-        <v>2.190196514129639</v>
+        <v>2.684319972991943</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3766,7 +3766,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D157">
-        <v>6.454610824584961</v>
+        <v>6.626244068145752</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3780,7 +3780,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D158">
-        <v>1.37708854675293</v>
+        <v>1.747752666473389</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3794,7 +3794,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D159">
-        <v>2.923413038253784</v>
+        <v>4.508416175842285</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3808,7 +3808,7 @@
         <v>9</v>
       </c>
       <c r="D160">
-        <v>2.93519139289856</v>
+        <v>3.28940224647522</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3822,7 +3822,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D161">
-        <v>1.446003317832947</v>
+        <v>1.840011119842529</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3836,7 +3836,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D162">
-        <v>1.377624750137329</v>
+        <v>2.194629669189453</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3850,7 +3850,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D163">
-        <v>4.772371292114258</v>
+        <v>4.250844955444336</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3864,7 +3864,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D164">
-        <v>1.648072481155396</v>
+        <v>1.962602376937866</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3878,7 +3878,7 @@
         <v>2</v>
       </c>
       <c r="D165">
-        <v>3.159103393554688</v>
+        <v>2.182809352874756</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3892,7 +3892,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D166">
-        <v>4.311465263366699</v>
+        <v>4.00200366973877</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3906,7 +3906,7 @@
         <v>4.5</v>
       </c>
       <c r="D167">
-        <v>1.574570655822754</v>
+        <v>1.984501481056213</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3920,7 +3920,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D168">
-        <v>2.759760856628418</v>
+        <v>2.228858470916748</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3934,7 +3934,7 @@
         <v>3.5</v>
       </c>
       <c r="D169">
-        <v>1.38467264175415</v>
+        <v>1.834893941879272</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3948,7 +3948,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D170">
-        <v>1.765003085136414</v>
+        <v>2.71595287322998</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3962,7 +3962,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D171">
-        <v>1.401523351669312</v>
+        <v>2.110693693161011</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3976,7 +3976,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D172">
-        <v>4.200971603393555</v>
+        <v>4.654227256774902</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3990,7 +3990,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D173">
-        <v>2.813304424285889</v>
+        <v>2.724277019500732</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4004,7 +4004,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D174">
-        <v>4.534187793731689</v>
+        <v>4.845188617706299</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4018,7 +4018,7 @@
         <v>2</v>
       </c>
       <c r="D175">
-        <v>1.554466485977173</v>
+        <v>2.537008285522461</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4032,7 +4032,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D176">
-        <v>3.132802724838257</v>
+        <v>2.367329120635986</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4046,7 +4046,7 @@
         <v>3</v>
       </c>
       <c r="D177">
-        <v>1.453545451164246</v>
+        <v>3.314217567443848</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4060,7 +4060,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D178">
-        <v>5.717892646789551</v>
+        <v>6.194137096405029</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4074,7 +4074,7 @@
         <v>28.39999961853027</v>
       </c>
       <c r="D179">
-        <v>13.36287117004395</v>
+        <v>14.28560829162598</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4088,7 +4088,7 @@
         <v>3</v>
       </c>
       <c r="D180">
-        <v>2.928323268890381</v>
+        <v>3.734879016876221</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4102,7 +4102,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D181">
-        <v>7.944403648376465</v>
+        <v>7.450204372406006</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4116,7 +4116,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D182">
-        <v>3.190698146820068</v>
+        <v>4.473499298095703</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4130,7 +4130,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D183">
-        <v>4.888454437255859</v>
+        <v>6.312501430511475</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4144,7 +4144,7 @@
         <v>8</v>
       </c>
       <c r="D184">
-        <v>7.294260501861572</v>
+        <v>6.080027103424072</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4158,7 +4158,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D185">
-        <v>1.359082818031311</v>
+        <v>1.251256823539734</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4172,7 +4172,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D186">
-        <v>5.769007205963135</v>
+        <v>5.881259441375732</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4186,7 +4186,7 @@
         <v>3</v>
       </c>
       <c r="D187">
-        <v>2.534234523773193</v>
+        <v>3.3705153465271</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4200,7 +4200,7 @@
         <v>4</v>
       </c>
       <c r="D188">
-        <v>1.400427460670471</v>
+        <v>1.783488988876343</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4214,7 +4214,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D189">
-        <v>1.634232521057129</v>
+        <v>1.844104409217834</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4228,7 +4228,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D190">
-        <v>2.380367040634155</v>
+        <v>2.912570953369141</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4242,7 +4242,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D191">
-        <v>1.35882306098938</v>
+        <v>1.587347865104675</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4256,7 +4256,7 @@
         <v>12.19999980926514</v>
       </c>
       <c r="D192">
-        <v>11.62720108032227</v>
+        <v>10.29248428344727</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4270,7 +4270,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D193">
-        <v>6.286289215087891</v>
+        <v>7.057311534881592</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4284,7 +4284,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D194">
-        <v>1.380542516708374</v>
+        <v>2.054176092147827</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4298,7 +4298,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D195">
-        <v>1.381908178329468</v>
+        <v>1.420374274253845</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4312,7 +4312,7 @@
         <v>17.39999961853027</v>
       </c>
       <c r="D196">
-        <v>13.31079483032227</v>
+        <v>12.44729614257812</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4326,7 +4326,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D197">
-        <v>4.641738891601562</v>
+        <v>3.439588785171509</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4340,7 +4340,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D198">
-        <v>1.35948657989502</v>
+        <v>1.222341418266296</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4354,7 +4354,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D199">
-        <v>5.223764896392822</v>
+        <v>5.252035617828369</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4368,7 +4368,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D200">
-        <v>1.436541795730591</v>
+        <v>1.96561861038208</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4382,7 +4382,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D201">
-        <v>1.385195970535278</v>
+        <v>2.990464210510254</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4396,7 +4396,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D202">
-        <v>1.381906628608704</v>
+        <v>1.827958345413208</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4410,7 +4410,7 @@
         <v>1.5</v>
       </c>
       <c r="D203">
-        <v>1.470170497894287</v>
+        <v>1.968450546264648</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4424,7 +4424,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D204">
-        <v>4.185935020446777</v>
+        <v>6.13673210144043</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4438,7 +4438,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D205">
-        <v>1.486475229263306</v>
+        <v>2.921652555465698</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4452,7 +4452,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D206">
-        <v>10.56294631958008</v>
+        <v>10.03703880310059</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4466,7 +4466,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D207">
-        <v>2.240952014923096</v>
+        <v>3.080304384231567</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4480,7 +4480,7 @@
         <v>3.5</v>
       </c>
       <c r="D208">
-        <v>4.023988723754883</v>
+        <v>3.603496074676514</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4494,7 +4494,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D209">
-        <v>1.853578329086304</v>
+        <v>3.333675146102905</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4508,7 +4508,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D210">
-        <v>2.678122043609619</v>
+        <v>2.970540046691895</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4522,7 +4522,7 @@
         <v>3.5</v>
       </c>
       <c r="D211">
-        <v>2.9264235496521</v>
+        <v>2.29895544052124</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4536,7 +4536,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D212">
-        <v>1.540700197219849</v>
+        <v>2.256349086761475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4550,7 +4550,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D213">
-        <v>1.781586170196533</v>
+        <v>2.939600467681885</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4564,7 +4564,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D214">
-        <v>2.56284236907959</v>
+        <v>3.008031606674194</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4578,7 +4578,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D215">
-        <v>1.872477412223816</v>
+        <v>1.994459629058838</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4592,7 +4592,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D216">
-        <v>1.602068424224854</v>
+        <v>2.492840528488159</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>2.332145690917969</v>
+        <v>2.621732473373413</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4620,7 +4620,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D218">
-        <v>1.352389097213745</v>
+        <v>2.451107025146484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4634,7 +4634,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D219">
-        <v>2.861245155334473</v>
+        <v>2.884927034378052</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4648,7 +4648,7 @@
         <v>1.5</v>
       </c>
       <c r="D220">
-        <v>1.627333641052246</v>
+        <v>2.116692543029785</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4662,7 +4662,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D221">
-        <v>4.282308101654053</v>
+        <v>4.222497940063477</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4676,7 +4676,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D222">
-        <v>1.764765858650208</v>
+        <v>1.861716032028198</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4690,7 +4690,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D223">
-        <v>2.5351402759552</v>
+        <v>4.189757823944092</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4704,7 +4704,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D224">
-        <v>1.615323543548584</v>
+        <v>1.884843826293945</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4718,7 +4718,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D225">
-        <v>1.480813503265381</v>
+        <v>1.929871678352356</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4732,7 +4732,7 @@
         <v>2</v>
       </c>
       <c r="D226">
-        <v>2.8526930809021</v>
+        <v>2.484046936035156</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4746,7 +4746,7 @@
         <v>0.5</v>
       </c>
       <c r="D227">
-        <v>2.298715353012085</v>
+        <v>2.533711910247803</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4760,7 +4760,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D228">
-        <v>2.955338001251221</v>
+        <v>2.094232559204102</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4774,7 +4774,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D229">
-        <v>5.541085243225098</v>
+        <v>4.805802345275879</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="D230">
-        <v>1.364950895309448</v>
+        <v>1.374763965606689</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4802,7 +4802,7 @@
         <v>1</v>
       </c>
       <c r="D231">
-        <v>3.074850559234619</v>
+        <v>2.263510942459106</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4816,7 +4816,7 @@
         <v>25</v>
       </c>
       <c r="D232">
-        <v>14.07233428955078</v>
+        <v>16.37954902648926</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4830,7 +4830,7 @@
         <v>0.5</v>
       </c>
       <c r="D233">
-        <v>1.50104820728302</v>
+        <v>2.401200532913208</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4844,7 +4844,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D234">
-        <v>1.642621517181396</v>
+        <v>1.901403069496155</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4858,7 +4858,7 @@
         <v>17</v>
       </c>
       <c r="D235">
-        <v>15.98239707946777</v>
+        <v>15.1553840637207</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4872,7 +4872,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D236">
-        <v>4.500965118408203</v>
+        <v>3.603898525238037</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4886,7 +4886,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D237">
-        <v>2.598381042480469</v>
+        <v>3.325655937194824</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4900,7 +4900,7 @@
         <v>20.5</v>
       </c>
       <c r="D238">
-        <v>18.26289939880371</v>
+        <v>16.1598072052002</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4914,7 +4914,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D239">
-        <v>1.355889320373535</v>
+        <v>1.606578350067139</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4928,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="D240">
-        <v>1.424363851547241</v>
+        <v>1.207284927368164</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4942,7 +4942,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D241">
-        <v>1.615220308303833</v>
+        <v>1.859606146812439</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4956,7 +4956,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D242">
-        <v>3.154600381851196</v>
+        <v>1.963968753814697</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4970,7 +4970,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D243">
-        <v>1.366004943847656</v>
+        <v>2.058945178985596</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4984,7 +4984,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D244">
-        <v>1.544723510742188</v>
+        <v>2.96476411819458</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4998,7 +4998,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D245">
-        <v>1.553310394287109</v>
+        <v>1.442062973976135</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5012,7 +5012,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D246">
-        <v>4.842696189880371</v>
+        <v>4.158487319946289</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5026,7 +5026,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D247">
-        <v>4.025635242462158</v>
+        <v>2.281563520431519</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5040,7 +5040,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D248">
-        <v>2.529107809066772</v>
+        <v>2.424853563308716</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5054,7 +5054,7 @@
         <v>22.60000038146973</v>
       </c>
       <c r="D249">
-        <v>4.457530975341797</v>
+        <v>7.056662559509277</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5068,7 +5068,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D250">
-        <v>2.476700305938721</v>
+        <v>3.990291118621826</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5082,7 +5082,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D251">
-        <v>4.873191833496094</v>
+        <v>3.94279670715332</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5096,7 +5096,7 @@
         <v>3.5</v>
       </c>
       <c r="D252">
-        <v>2.603386402130127</v>
+        <v>3.399763345718384</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5110,7 +5110,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D253">
-        <v>1.399987459182739</v>
+        <v>2.369717359542847</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5124,7 +5124,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D254">
-        <v>3.034911155700684</v>
+        <v>3.32271146774292</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5138,7 +5138,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D255">
-        <v>5.530783176422119</v>
+        <v>4.833069801330566</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5152,7 +5152,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D256">
-        <v>1.385932564735413</v>
+        <v>1.844820499420166</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5166,7 +5166,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D257">
-        <v>1.817510485649109</v>
+        <v>1.700812101364136</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5180,7 +5180,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D258">
-        <v>1.69654393196106</v>
+        <v>2.163766384124756</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5194,7 +5194,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D259">
-        <v>1.353704571723938</v>
+        <v>1.675931692123413</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5208,7 +5208,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D260">
-        <v>2.549947738647461</v>
+        <v>2.987129211425781</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5222,7 +5222,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D261">
-        <v>1.374724984169006</v>
+        <v>2.368574380874634</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5236,7 +5236,7 @@
         <v>1</v>
       </c>
       <c r="D262">
-        <v>1.573907256126404</v>
+        <v>2.466186761856079</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5250,7 +5250,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D263">
-        <v>4.76022481918335</v>
+        <v>3.853143930435181</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5264,7 +5264,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D264">
-        <v>3.4067702293396</v>
+        <v>3.24376916885376</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5278,7 +5278,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D265">
-        <v>2.11745285987854</v>
+        <v>2.00750732421875</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5292,7 +5292,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D266">
-        <v>1.913168668746948</v>
+        <v>2.550002574920654</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5306,7 +5306,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D267">
-        <v>1.409648060798645</v>
+        <v>1.848385095596313</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5320,7 +5320,7 @@
         <v>37.20000076293945</v>
       </c>
       <c r="D268">
-        <v>22.44522857666016</v>
+        <v>22.64383125305176</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5334,7 +5334,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D269">
-        <v>1.791664481163025</v>
+        <v>3.34865140914917</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5348,7 +5348,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D270">
-        <v>1.481965065002441</v>
+        <v>3.215833425521851</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5362,7 +5362,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D271">
-        <v>3.084121465682983</v>
+        <v>3.435943603515625</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5376,7 +5376,7 @@
         <v>1.5</v>
       </c>
       <c r="D272">
-        <v>1.494984269142151</v>
+        <v>1.811401724815369</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5390,7 +5390,7 @@
         <v>0.5</v>
       </c>
       <c r="D273">
-        <v>1.580066204071045</v>
+        <v>3.261413335800171</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5404,7 +5404,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D274">
-        <v>6.385197639465332</v>
+        <v>7.384548187255859</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5418,7 +5418,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D275">
-        <v>2.761627912521362</v>
+        <v>2.510055541992188</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5432,7 +5432,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D276">
-        <v>5.366602897644043</v>
+        <v>5.656762599945068</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5446,7 +5446,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D277">
-        <v>1.398416996002197</v>
+        <v>1.929908156394958</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5460,7 +5460,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D278">
-        <v>6.245610237121582</v>
+        <v>6.066239356994629</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5474,7 +5474,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D279">
-        <v>2.15352725982666</v>
+        <v>2.192514419555664</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5488,7 +5488,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D280">
-        <v>2.899014472961426</v>
+        <v>3.674120187759399</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5502,7 +5502,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D281">
-        <v>10.88298416137695</v>
+        <v>11.68180084228516</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5516,7 +5516,7 @@
         <v>15.60000038146973</v>
       </c>
       <c r="D282">
-        <v>9.446164131164551</v>
+        <v>10.76989936828613</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5530,7 +5530,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D283">
-        <v>1.35409414768219</v>
+        <v>1.509657859802246</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5544,7 +5544,7 @@
         <v>5</v>
       </c>
       <c r="D284">
-        <v>5.692829132080078</v>
+        <v>4.655784130096436</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5558,7 +5558,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D285">
-        <v>2.33864164352417</v>
+        <v>2.127051830291748</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5572,7 +5572,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D286">
-        <v>1.356838464736938</v>
+        <v>1.423676729202271</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5586,7 +5586,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D287">
-        <v>3.449814319610596</v>
+        <v>3.456900358200073</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5600,7 +5600,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D288">
-        <v>5.336936950683594</v>
+        <v>4.816219329833984</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5614,7 +5614,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D289">
-        <v>1.713196516036987</v>
+        <v>1.709730267524719</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5628,7 +5628,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D290">
-        <v>8.235469818115234</v>
+        <v>7.915257930755615</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5642,7 +5642,7 @@
         <v>2.5</v>
       </c>
       <c r="D291">
-        <v>1.809749603271484</v>
+        <v>3.061191082000732</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5656,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>2.334751605987549</v>
+        <v>3.887032270431519</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5670,7 +5670,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D293">
-        <v>2.588489294052124</v>
+        <v>2.64292049407959</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5684,7 +5684,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D294">
-        <v>4.288120269775391</v>
+        <v>4.02593994140625</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5698,7 +5698,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D295">
-        <v>4.884542465209961</v>
+        <v>4.354445457458496</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5712,7 +5712,7 @@
         <v>6</v>
       </c>
       <c r="D296">
-        <v>1.648971557617188</v>
+        <v>2.072498798370361</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5726,7 +5726,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D297">
-        <v>3.177480459213257</v>
+        <v>2.112998247146606</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5740,7 +5740,7 @@
         <v>9.5</v>
       </c>
       <c r="D298">
-        <v>11.13401031494141</v>
+        <v>13.48546981811523</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5754,7 +5754,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D299">
-        <v>1.687621355056763</v>
+        <v>1.809484243392944</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5768,7 +5768,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D300">
-        <v>4.275722980499268</v>
+        <v>7.902407169342041</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5782,7 +5782,7 @@
         <v>9</v>
       </c>
       <c r="D301">
-        <v>2.650538921356201</v>
+        <v>3.612974643707275</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5796,7 +5796,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D302">
-        <v>2.920978307723999</v>
+        <v>2.763869285583496</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5810,7 +5810,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D303">
-        <v>1.43742561340332</v>
+        <v>3.045181274414062</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5824,7 +5824,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D304">
-        <v>1.387694835662842</v>
+        <v>2.529777050018311</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5838,7 +5838,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D305">
-        <v>1.521721124649048</v>
+        <v>3.430175304412842</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5852,7 +5852,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D306">
-        <v>2.026381254196167</v>
+        <v>4.419348239898682</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5866,7 +5866,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D307">
-        <v>5.516631126403809</v>
+        <v>4.695526599884033</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5880,7 +5880,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D308">
-        <v>1.391652703285217</v>
+        <v>1.872130990028381</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5894,7 +5894,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="D309">
-        <v>1.864933967590332</v>
+        <v>1.916388511657715</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5908,7 +5908,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D310">
-        <v>2.855188846588135</v>
+        <v>2.488090515136719</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5922,7 +5922,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D311">
-        <v>2.480430364608765</v>
+        <v>2.103595972061157</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5936,7 +5936,7 @@
         <v>2.5</v>
       </c>
       <c r="D312">
-        <v>2.064305782318115</v>
+        <v>2.395860910415649</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5950,7 +5950,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D313">
-        <v>1.407472014427185</v>
+        <v>1.498357653617859</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5964,7 +5964,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D314">
-        <v>2.144270420074463</v>
+        <v>1.745325803756714</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5978,7 +5978,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D315">
-        <v>1.650146842002869</v>
+        <v>1.404119729995728</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5992,7 +5992,7 @@
         <v>1</v>
       </c>
       <c r="D316">
-        <v>1.483786821365356</v>
+        <v>1.969700336456299</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6006,7 +6006,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D317">
-        <v>1.365440845489502</v>
+        <v>1.311838030815125</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6020,7 +6020,7 @@
         <v>8.5</v>
       </c>
       <c r="D318">
-        <v>3.258687734603882</v>
+        <v>4.302370071411133</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -6034,7 +6034,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D319">
-        <v>5.488794803619385</v>
+        <v>3.723620891571045</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -6048,7 +6048,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D320">
-        <v>7.889445304870605</v>
+        <v>6.918138980865479</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -6062,7 +6062,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D321">
-        <v>10.63071346282959</v>
+        <v>11.24563598632812</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -6076,7 +6076,7 @@
         <v>4</v>
       </c>
       <c r="D322">
-        <v>2.928656339645386</v>
+        <v>2.206350564956665</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -6090,7 +6090,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D323">
-        <v>1.992071151733398</v>
+        <v>1.807352185249329</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -6104,7 +6104,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D324">
-        <v>8.73082447052002</v>
+        <v>7.787187576293945</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -6118,7 +6118,7 @@
         <v>17.89999961853027</v>
       </c>
       <c r="D325">
-        <v>15.4881477355957</v>
+        <v>15.62502861022949</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -6132,7 +6132,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D326">
-        <v>4.682258605957031</v>
+        <v>4.24507474899292</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -6146,7 +6146,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D327">
-        <v>1.396068453788757</v>
+        <v>1.720696926116943</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6160,7 +6160,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D328">
-        <v>2.683350801467896</v>
+        <v>2.01759147644043</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6174,7 +6174,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D329">
-        <v>1.432692766189575</v>
+        <v>1.883819818496704</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6188,7 +6188,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D330">
-        <v>2.028307676315308</v>
+        <v>1.474436521530151</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6202,7 +6202,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D331">
-        <v>1.37245762348175</v>
+        <v>1.891759991645813</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6216,7 +6216,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D332">
-        <v>1.679744720458984</v>
+        <v>2.515016794204712</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6230,7 +6230,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D333">
-        <v>2.429611921310425</v>
+        <v>1.93509316444397</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6244,7 +6244,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D334">
-        <v>2.220511436462402</v>
+        <v>1.840736150741577</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6258,7 +6258,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D335">
-        <v>1.404927611351013</v>
+        <v>2.505038738250732</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6272,7 +6272,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D336">
-        <v>1.890500545501709</v>
+        <v>2.488972663879395</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6286,7 +6286,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D337">
-        <v>1.601072788238525</v>
+        <v>2.305716037750244</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6300,7 +6300,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D338">
-        <v>1.414201974868774</v>
+        <v>1.881396770477295</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6314,7 +6314,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D339">
-        <v>1.920265913009644</v>
+        <v>2.126183748245239</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6328,7 +6328,7 @@
         <v>23.20000076293945</v>
       </c>
       <c r="D340">
-        <v>11.06262969970703</v>
+        <v>11.12489128112793</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6342,7 +6342,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D341">
-        <v>1.476080656051636</v>
+        <v>1.813891172409058</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6356,7 +6356,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D342">
-        <v>2.845206260681152</v>
+        <v>2.415127277374268</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6370,7 +6370,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D343">
-        <v>1.385566234588623</v>
+        <v>2.164407730102539</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6384,7 +6384,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D344">
-        <v>2.254736661911011</v>
+        <v>2.808032035827637</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6398,7 +6398,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D345">
-        <v>2.97239351272583</v>
+        <v>2.933638334274292</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6412,7 +6412,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D346">
-        <v>6.225396156311035</v>
+        <v>6.472473621368408</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6426,7 +6426,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D347">
-        <v>5.477900505065918</v>
+        <v>4.672805309295654</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6440,7 +6440,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D348">
-        <v>5.586092472076416</v>
+        <v>4.670806884765625</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6454,7 +6454,7 @@
         <v>3</v>
       </c>
       <c r="D349">
-        <v>1.764486908912659</v>
+        <v>2.616414070129395</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6468,7 +6468,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D350">
-        <v>1.498058199882507</v>
+        <v>2.050304412841797</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6482,7 +6482,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D351">
-        <v>1.873811721801758</v>
+        <v>2.748923778533936</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6496,7 +6496,7 @@
         <v>0.5</v>
       </c>
       <c r="D352">
-        <v>1.376100182533264</v>
+        <v>1.296078681945801</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6510,7 +6510,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D353">
-        <v>2.601945400238037</v>
+        <v>3.836649656295776</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6524,7 +6524,7 @@
         <v>3.5</v>
       </c>
       <c r="D354">
-        <v>2.925636768341064</v>
+        <v>2.069940090179443</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6538,7 +6538,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D355">
-        <v>3.147369861602783</v>
+        <v>3.271503448486328</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6552,7 +6552,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D356">
-        <v>5.464579582214355</v>
+        <v>3.229797124862671</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6566,7 +6566,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D357">
-        <v>5.439186573028564</v>
+        <v>4.208901405334473</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6580,7 +6580,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D358">
-        <v>1.358669757843018</v>
+        <v>1.216021299362183</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6594,7 +6594,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D359">
-        <v>1.383725762367249</v>
+        <v>1.337946176528931</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6608,7 +6608,7 @@
         <v>1</v>
       </c>
       <c r="D360">
-        <v>1.698482275009155</v>
+        <v>3.123246431350708</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6622,7 +6622,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D361">
-        <v>1.936071753501892</v>
+        <v>3.791574001312256</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6636,7 +6636,7 @@
         <v>4.5</v>
       </c>
       <c r="D362">
-        <v>2.777939319610596</v>
+        <v>1.9037766456604</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6650,7 +6650,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D363">
-        <v>1.79925000667572</v>
+        <v>4.01137638092041</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6664,7 +6664,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D364">
-        <v>1.354858160018921</v>
+        <v>1.708126664161682</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6678,7 +6678,7 @@
         <v>35.09999847412109</v>
       </c>
       <c r="D365">
-        <v>28.27845191955566</v>
+        <v>24.85182762145996</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6692,7 +6692,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D366">
-        <v>1.371686935424805</v>
+        <v>1.708355188369751</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6706,7 +6706,7 @@
         <v>4</v>
       </c>
       <c r="D367">
-        <v>2.269548416137695</v>
+        <v>2.793288230895996</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6720,7 +6720,7 @@
         <v>2</v>
       </c>
       <c r="D368">
-        <v>1.365108966827393</v>
+        <v>1.22458815574646</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6734,7 +6734,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D369">
-        <v>3.177721738815308</v>
+        <v>4.058523178100586</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6748,7 +6748,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D370">
-        <v>1.712944865226746</v>
+        <v>3.052330255508423</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6762,7 +6762,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D371">
-        <v>1.789918899536133</v>
+        <v>2.224160671234131</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6776,7 +6776,7 @@
         <v>2.5</v>
       </c>
       <c r="D372">
-        <v>1.651863574981689</v>
+        <v>2.059111356735229</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6790,7 +6790,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D373">
-        <v>2.370698928833008</v>
+        <v>2.59692645072937</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6804,7 +6804,7 @@
         <v>1.5</v>
       </c>
       <c r="D374">
-        <v>5.008296012878418</v>
+        <v>5.669606685638428</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6818,7 +6818,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D375">
-        <v>5.924837112426758</v>
+        <v>5.770151138305664</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6832,7 +6832,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D376">
-        <v>5.009493350982666</v>
+        <v>4.958437442779541</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6846,7 +6846,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D377">
-        <v>4.945947647094727</v>
+        <v>5.210626602172852</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6860,7 +6860,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D378">
-        <v>1.392542481422424</v>
+        <v>2.542841911315918</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6874,7 +6874,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D379">
-        <v>1.407985687255859</v>
+        <v>1.811623573303223</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6888,7 +6888,7 @@
         <v>2.5</v>
       </c>
       <c r="D380">
-        <v>1.981769204139709</v>
+        <v>3.023733615875244</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6902,7 +6902,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D381">
-        <v>1.575411200523376</v>
+        <v>1.728530287742615</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6916,7 +6916,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D382">
-        <v>3.491077899932861</v>
+        <v>4.033441543579102</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6930,7 +6930,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D383">
-        <v>2.324644088745117</v>
+        <v>2.442386627197266</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6944,7 +6944,7 @@
         <v>12.69999980926514</v>
       </c>
       <c r="D384">
-        <v>2.166438579559326</v>
+        <v>3.708219051361084</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6958,7 +6958,7 @@
         <v>25.10000038146973</v>
       </c>
       <c r="D385">
-        <v>22.61923027038574</v>
+        <v>20.77856636047363</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -6972,7 +6972,7 @@
         <v>4.5</v>
       </c>
       <c r="D386">
-        <v>2.20449686050415</v>
+        <v>1.518172740936279</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -6986,7 +6986,7 @@
         <v>8</v>
       </c>
       <c r="D387">
-        <v>4.841386795043945</v>
+        <v>4.857542991638184</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -7000,7 +7000,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D388">
-        <v>1.38918936252594</v>
+        <v>2.045798301696777</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -7014,7 +7014,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D389">
-        <v>1.396246194839478</v>
+        <v>2.047144174575806</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -7028,7 +7028,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D390">
-        <v>1.383232474327087</v>
+        <v>1.81741189956665</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -7042,7 +7042,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D391">
-        <v>6.010404586791992</v>
+        <v>8.276829719543457</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -7056,7 +7056,7 @@
         <v>19</v>
       </c>
       <c r="D392">
-        <v>15.2846508026123</v>
+        <v>17.69308662414551</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -7070,7 +7070,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D393">
-        <v>3.080682516098022</v>
+        <v>3.160913467407227</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -7084,7 +7084,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D394">
-        <v>1.387476205825806</v>
+        <v>1.731126427650452</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -7098,7 +7098,7 @@
         <v>12</v>
       </c>
       <c r="D395">
-        <v>5.274888515472412</v>
+        <v>5.924999713897705</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -7112,7 +7112,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D396">
-        <v>2.933103322982788</v>
+        <v>2.666137218475342</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -7126,7 +7126,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D397">
-        <v>6.53255558013916</v>
+        <v>4.631955623626709</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -7140,7 +7140,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D398">
-        <v>6.409871101379395</v>
+        <v>6.691170692443848</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7154,7 +7154,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D399">
-        <v>1.440511226654053</v>
+        <v>2.715142011642456</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7168,7 +7168,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D400">
-        <v>1.772032141685486</v>
+        <v>1.893891096115112</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7182,7 +7182,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D401">
-        <v>1.35061252117157</v>
+        <v>1.759958744049072</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7196,7 +7196,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D402">
-        <v>5.678666114807129</v>
+        <v>5.795944690704346</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7210,7 +7210,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D403">
-        <v>2.54462194442749</v>
+        <v>7.464442253112793</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7224,7 +7224,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D404">
-        <v>3.017089128494263</v>
+        <v>5.569617748260498</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7238,7 +7238,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D405">
-        <v>1.356934309005737</v>
+        <v>1.198930263519287</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7252,7 +7252,7 @@
         <v>3</v>
       </c>
       <c r="D406">
-        <v>2.021042823791504</v>
+        <v>2.15813946723938</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7266,7 +7266,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D407">
-        <v>1.850841879844666</v>
+        <v>1.8020339012146</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7280,7 +7280,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D408">
-        <v>2.115865707397461</v>
+        <v>1.931931853294373</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7294,7 +7294,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D409">
-        <v>9.068301200866699</v>
+        <v>8.95006275177002</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7308,7 +7308,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D410">
-        <v>1.356353998184204</v>
+        <v>1.212709069252014</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7322,7 +7322,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D411">
-        <v>2.709540605545044</v>
+        <v>2.057138919830322</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7336,7 +7336,7 @@
         <v>1.5</v>
       </c>
       <c r="D412">
-        <v>2.725880146026611</v>
+        <v>2.24300479888916</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7350,7 +7350,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D413">
-        <v>1.356632351875305</v>
+        <v>1.270708084106445</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7364,7 +7364,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D414">
-        <v>4.203691482543945</v>
+        <v>3.799658060073853</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7378,7 +7378,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D415">
-        <v>6.274503707885742</v>
+        <v>6.711781978607178</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7392,7 +7392,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D416">
-        <v>1.428340792655945</v>
+        <v>1.658729910850525</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7406,7 +7406,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D417">
-        <v>4.120498180389404</v>
+        <v>7.136826038360596</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7420,7 +7420,7 @@
         <v>5</v>
       </c>
       <c r="D418">
-        <v>2.620126247406006</v>
+        <v>1.712063312530518</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7434,7 +7434,7 @@
         <v>13</v>
       </c>
       <c r="D419">
-        <v>11.68374252319336</v>
+        <v>9.583639144897461</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7448,7 +7448,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D420">
-        <v>3.294406175613403</v>
+        <v>2.891974449157715</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7462,7 +7462,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D421">
-        <v>4.830840587615967</v>
+        <v>6.43174409866333</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7476,7 +7476,7 @@
         <v>22</v>
       </c>
       <c r="D422">
-        <v>15.31202697753906</v>
+        <v>14.47907257080078</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7490,7 +7490,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D423">
-        <v>1.356958150863647</v>
+        <v>1.249714374542236</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7504,7 +7504,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D424">
-        <v>1.361702561378479</v>
+        <v>3.174453496932983</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7518,7 +7518,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D425">
-        <v>7.399985313415527</v>
+        <v>7.497863292694092</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7532,7 +7532,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D426">
-        <v>2.451560735702515</v>
+        <v>1.904222011566162</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7546,7 +7546,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D427">
-        <v>1.359996795654297</v>
+        <v>1.239669680595398</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7560,7 +7560,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D428">
-        <v>1.529793381690979</v>
+        <v>1.759108781814575</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7574,7 +7574,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D429">
-        <v>5.734110832214355</v>
+        <v>5.430357456207275</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7588,7 +7588,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D430">
-        <v>4.131685256958008</v>
+        <v>4.184514045715332</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7602,7 +7602,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D431">
-        <v>6.996172904968262</v>
+        <v>7.175303936004639</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7616,7 +7616,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D432">
-        <v>1.360285639762878</v>
+        <v>1.515511274337769</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7630,7 +7630,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D433">
-        <v>2.945499420166016</v>
+        <v>2.17451548576355</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7644,7 +7644,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D434">
-        <v>1.574342966079712</v>
+        <v>1.506012678146362</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7658,7 +7658,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D435">
-        <v>1.697855710983276</v>
+        <v>2.744904041290283</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7672,7 +7672,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D436">
-        <v>3.404539108276367</v>
+        <v>5.005251884460449</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7686,7 +7686,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D437">
-        <v>1.389975070953369</v>
+        <v>1.851593017578125</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7700,7 +7700,7 @@
         <v>19.70000076293945</v>
       </c>
       <c r="D438">
-        <v>8.383237838745117</v>
+        <v>9.550445556640625</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7714,7 +7714,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D439">
-        <v>3.009778022766113</v>
+        <v>3.203708648681641</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7728,7 +7728,7 @@
         <v>0</v>
       </c>
       <c r="D440">
-        <v>1.481460452079773</v>
+        <v>1.668934226036072</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7742,7 +7742,7 @@
         <v>9</v>
       </c>
       <c r="D441">
-        <v>3.767541408538818</v>
+        <v>4.734298229217529</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7756,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="D442">
-        <v>1.401343584060669</v>
+        <v>3.198028087615967</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7770,7 +7770,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D443">
-        <v>1.705670595169067</v>
+        <v>2.951846361160278</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7784,7 +7784,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D444">
-        <v>2.137632131576538</v>
+        <v>1.856234550476074</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7798,7 +7798,7 @@
         <v>6</v>
       </c>
       <c r="D445">
-        <v>2.376343488693237</v>
+        <v>2.374500751495361</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7812,7 +7812,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D446">
-        <v>5.072071075439453</v>
+        <v>2.583133697509766</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7826,7 +7826,7 @@
         <v>3</v>
       </c>
       <c r="D447">
-        <v>2.037833690643311</v>
+        <v>1.951896667480469</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7840,7 +7840,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D448">
-        <v>1.626881957054138</v>
+        <v>1.923536658287048</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7854,7 +7854,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D449">
-        <v>2.983212471008301</v>
+        <v>5.257894992828369</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7868,7 +7868,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D450">
-        <v>1.982732057571411</v>
+        <v>2.607912540435791</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7882,7 +7882,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D451">
-        <v>3.065173387527466</v>
+        <v>2.367815017700195</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7896,7 +7896,7 @@
         <v>2</v>
       </c>
       <c r="D452">
-        <v>1.391349792480469</v>
+        <v>1.852465510368347</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7910,7 +7910,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D453">
-        <v>5.212047576904297</v>
+        <v>4.642096996307373</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7924,7 +7924,7 @@
         <v>0</v>
       </c>
       <c r="D454">
-        <v>1.405163288116455</v>
+        <v>1.703442454338074</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7938,7 +7938,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D455">
-        <v>1.485647082328796</v>
+        <v>1.726906657218933</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7952,7 +7952,7 @@
         <v>13</v>
       </c>
       <c r="D456">
-        <v>8.888895988464355</v>
+        <v>11.88410568237305</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7966,7 +7966,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D457">
-        <v>4.360398292541504</v>
+        <v>3.748093605041504</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -7980,7 +7980,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D458">
-        <v>1.418208599090576</v>
+        <v>1.619694232940674</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -7994,7 +7994,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D459">
-        <v>3.019601345062256</v>
+        <v>3.090257167816162</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -8008,7 +8008,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D460">
-        <v>2.888210296630859</v>
+        <v>2.96751070022583</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -8022,7 +8022,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D461">
-        <v>1.999026417732239</v>
+        <v>2.466268062591553</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -8036,7 +8036,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D462">
-        <v>1.367512941360474</v>
+        <v>1.50360107421875</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -8050,7 +8050,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D463">
-        <v>1.373480677604675</v>
+        <v>2.406769990921021</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -8064,7 +8064,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D464">
-        <v>3.468354225158691</v>
+        <v>2.72550630569458</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -8078,7 +8078,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D465">
-        <v>4.146461009979248</v>
+        <v>3.86084771156311</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -8092,7 +8092,7 @@
         <v>0.5</v>
       </c>
       <c r="D466">
-        <v>1.73913586139679</v>
+        <v>2.064856767654419</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -8106,7 +8106,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D467">
-        <v>3.076995372772217</v>
+        <v>2.070021152496338</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -8120,7 +8120,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D468">
-        <v>1.524470686912537</v>
+        <v>2.015982151031494</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -8134,7 +8134,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D469">
-        <v>2.071854591369629</v>
+        <v>1.787396192550659</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -8148,7 +8148,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D470">
-        <v>3.621067523956299</v>
+        <v>3.797942638397217</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8162,7 +8162,7 @@
         <v>3.5</v>
       </c>
       <c r="D471">
-        <v>1.688383340835571</v>
+        <v>3.128790378570557</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8176,7 +8176,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D472">
-        <v>2.341280221939087</v>
+        <v>2.676248788833618</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8190,7 +8190,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D473">
-        <v>1.357474327087402</v>
+        <v>1.561025857925415</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8204,7 +8204,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D474">
-        <v>3.44407320022583</v>
+        <v>3.233700275421143</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8218,7 +8218,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D475">
-        <v>6.441330909729004</v>
+        <v>3.942969560623169</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8232,7 +8232,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D476">
-        <v>8.104631423950195</v>
+        <v>16.55331993103027</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8246,7 +8246,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D477">
-        <v>1.401885867118835</v>
+        <v>1.774345636367798</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8260,7 +8260,7 @@
         <v>2.5</v>
       </c>
       <c r="D478">
-        <v>2.23769736289978</v>
+        <v>3.55101490020752</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8274,7 +8274,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D479">
-        <v>1.509263753890991</v>
+        <v>1.815710425376892</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8288,7 +8288,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D480">
-        <v>2.550332307815552</v>
+        <v>3.266710996627808</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8302,7 +8302,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D481">
-        <v>1.395609974861145</v>
+        <v>1.892518162727356</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8316,7 +8316,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D482">
-        <v>2.842162132263184</v>
+        <v>3.413677215576172</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8330,7 +8330,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D483">
-        <v>1.353386163711548</v>
+        <v>2.44919753074646</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8344,7 +8344,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D484">
-        <v>2.499277114868164</v>
+        <v>2.528229713439941</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8358,7 +8358,7 @@
         <v>36.09999847412109</v>
       </c>
       <c r="D485">
-        <v>19.21787643432617</v>
+        <v>21.97328948974609</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8372,7 +8372,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D486">
-        <v>1.369325637817383</v>
+        <v>1.984796285629272</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8386,7 +8386,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D487">
-        <v>2.913470268249512</v>
+        <v>3.805340051651001</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8400,7 +8400,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D488">
-        <v>1.75268030166626</v>
+        <v>2.031148433685303</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8414,7 +8414,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D489">
-        <v>1.751806735992432</v>
+        <v>2.66514253616333</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8428,7 +8428,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D490">
-        <v>3.273534536361694</v>
+        <v>3.046855926513672</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8442,7 +8442,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D491">
-        <v>2.501785755157471</v>
+        <v>3.160443782806396</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8456,7 +8456,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D492">
-        <v>5.02225399017334</v>
+        <v>3.446385383605957</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8470,7 +8470,7 @@
         <v>3</v>
       </c>
       <c r="D493">
-        <v>3.042747974395752</v>
+        <v>2.276367425918579</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8484,7 +8484,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D494">
-        <v>1.97662627696991</v>
+        <v>2.433347702026367</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8498,7 +8498,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D495">
-        <v>2.679422855377197</v>
+        <v>2.932950973510742</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8512,7 +8512,7 @@
         <v>0.5</v>
       </c>
       <c r="D496">
-        <v>1.356669425964355</v>
+        <v>1.478464007377625</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8526,7 +8526,7 @@
         <v>2</v>
       </c>
       <c r="D497">
-        <v>2.043731212615967</v>
+        <v>3.043127775192261</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8540,7 +8540,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D498">
-        <v>1.393785357475281</v>
+        <v>1.905048370361328</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8554,7 +8554,7 @@
         <v>13</v>
       </c>
       <c r="D499">
-        <v>2.338106155395508</v>
+        <v>2.029583930969238</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8568,7 +8568,7 @@
         <v>7</v>
       </c>
       <c r="D500">
-        <v>2.766690015792847</v>
+        <v>2.248645782470703</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8582,7 +8582,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D501">
-        <v>2.668575286865234</v>
+        <v>2.732073307037354</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8596,7 +8596,7 @@
         <v>8.5</v>
       </c>
       <c r="D502">
-        <v>7.726884841918945</v>
+        <v>8.971187591552734</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8610,7 +8610,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D503">
-        <v>2.912110805511475</v>
+        <v>2.426394701004028</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8624,7 +8624,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D504">
-        <v>4.124992847442627</v>
+        <v>3.852871894836426</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8638,7 +8638,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D505">
-        <v>1.459788918495178</v>
+        <v>2.426535606384277</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8652,7 +8652,7 @@
         <v>6.5</v>
       </c>
       <c r="D506">
-        <v>2.216740131378174</v>
+        <v>2.20983099937439</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8666,7 +8666,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D507">
-        <v>1.419689059257507</v>
+        <v>2.136172533035278</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8680,7 +8680,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D508">
-        <v>1.507043242454529</v>
+        <v>1.856404900550842</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8694,7 +8694,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D509">
-        <v>3.795569896697998</v>
+        <v>5.421394348144531</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8708,7 +8708,7 @@
         <v>3</v>
       </c>
       <c r="D510">
-        <v>1.936578631401062</v>
+        <v>1.817184209823608</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8722,7 +8722,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D511">
-        <v>3.787331581115723</v>
+        <v>4.499887466430664</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8736,7 +8736,7 @@
         <v>32.5</v>
       </c>
       <c r="D512">
-        <v>18.00829887390137</v>
+        <v>16.68370246887207</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8750,7 +8750,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D513">
-        <v>2.254462957382202</v>
+        <v>3.594324111938477</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8764,7 +8764,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D514">
-        <v>2.337236881256104</v>
+        <v>2.298095703125</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8778,7 +8778,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D515">
-        <v>2.449585437774658</v>
+        <v>2.641905069351196</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8792,7 +8792,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D516">
-        <v>1.402742266654968</v>
+        <v>1.985922813415527</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8806,7 +8806,7 @@
         <v>1.5</v>
       </c>
       <c r="D517">
-        <v>1.351172685623169</v>
+        <v>1.577159404754639</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8820,7 +8820,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D518">
-        <v>2.549188137054443</v>
+        <v>1.931852221488953</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8834,7 +8834,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D519">
-        <v>5.250350475311279</v>
+        <v>8.233600616455078</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8848,7 +8848,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D520">
-        <v>4.920852661132812</v>
+        <v>4.823713302612305</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8862,7 +8862,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D521">
-        <v>10.95874214172363</v>
+        <v>11.35864639282227</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8876,7 +8876,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D522">
-        <v>2.290456295013428</v>
+        <v>2.32764720916748</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8890,7 +8890,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D523">
-        <v>8.185404777526855</v>
+        <v>9.150180816650391</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8904,7 +8904,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D524">
-        <v>1.398705005645752</v>
+        <v>1.725719690322876</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8918,7 +8918,7 @@
         <v>15.39999961853027</v>
       </c>
       <c r="D525">
-        <v>12.83782005310059</v>
+        <v>13.36929321289062</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8932,7 +8932,7 @@
         <v>3</v>
       </c>
       <c r="D526">
-        <v>2.53493857383728</v>
+        <v>2.173113346099854</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8946,7 +8946,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D527">
-        <v>5.585700511932373</v>
+        <v>4.787360668182373</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8960,7 +8960,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D528">
-        <v>3.039641141891479</v>
+        <v>4.164986133575439</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -8974,7 +8974,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D529">
-        <v>1.872726440429688</v>
+        <v>2.194236278533936</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -8988,7 +8988,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D530">
-        <v>1.511229038238525</v>
+        <v>3.695880174636841</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9002,7 +9002,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D531">
-        <v>3.388864517211914</v>
+        <v>2.399659156799316</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9016,7 +9016,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D532">
-        <v>1.3748779296875</v>
+        <v>1.324729204177856</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -9030,7 +9030,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D533">
-        <v>2.838779449462891</v>
+        <v>1.70258104801178</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9044,7 +9044,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D534">
-        <v>1.377347946166992</v>
+        <v>1.79754638671875</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9058,7 +9058,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D535">
-        <v>5.894201278686523</v>
+        <v>6.686200618743896</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -9072,7 +9072,7 @@
         <v>26</v>
       </c>
       <c r="D536">
-        <v>15.79440116882324</v>
+        <v>14.48435401916504</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -9086,7 +9086,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D537">
-        <v>5.209421634674072</v>
+        <v>4.661591529846191</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9100,7 +9100,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D538">
-        <v>1.504402875900269</v>
+        <v>2.041502952575684</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9114,7 +9114,7 @@
         <v>15.89999961853027</v>
       </c>
       <c r="D539">
-        <v>9.547901153564453</v>
+        <v>8.970612525939941</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9128,7 +9128,7 @@
         <v>27.5</v>
       </c>
       <c r="D540">
-        <v>12.11977481842041</v>
+        <v>12.29851913452148</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9142,7 +9142,7 @@
         <v>6</v>
       </c>
       <c r="D541">
-        <v>2.625453472137451</v>
+        <v>2.82735800743103</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -9156,7 +9156,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D542">
-        <v>3.139691829681396</v>
+        <v>5.343522548675537</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9170,7 +9170,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D543">
-        <v>1.551134586334229</v>
+        <v>3.318611621856689</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9184,7 +9184,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D544">
-        <v>1.415594696998596</v>
+        <v>1.901552438735962</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9198,7 +9198,7 @@
         <v>1.5</v>
       </c>
       <c r="D545">
-        <v>2.233605861663818</v>
+        <v>3.074342012405396</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9212,7 +9212,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D546">
-        <v>1.490935683250427</v>
+        <v>3.626224040985107</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9226,7 +9226,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D547">
-        <v>8.001551628112793</v>
+        <v>8.218002319335938</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9240,7 +9240,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D548">
-        <v>3.189533710479736</v>
+        <v>2.118891716003418</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9254,7 +9254,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D549">
-        <v>2.393407344818115</v>
+        <v>1.810951113700867</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9268,7 +9268,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D550">
-        <v>3.18622612953186</v>
+        <v>4.351616382598877</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9282,7 +9282,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D551">
-        <v>5.345526695251465</v>
+        <v>4.853096008300781</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9296,7 +9296,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D552">
-        <v>5.832560539245605</v>
+        <v>6.393342018127441</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9310,7 +9310,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D553">
-        <v>1.631708383560181</v>
+        <v>2.020594120025635</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9324,7 +9324,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D554">
-        <v>1.585333228111267</v>
+        <v>2.174914121627808</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -9338,7 +9338,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D555">
-        <v>1.367842316627502</v>
+        <v>1.338326930999756</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -9352,7 +9352,7 @@
         <v>2</v>
       </c>
       <c r="D556">
-        <v>1.942914843559265</v>
+        <v>2.338191986083984</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9366,7 +9366,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D557">
-        <v>2.251237392425537</v>
+        <v>2.368517875671387</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -9380,7 +9380,7 @@
         <v>6</v>
       </c>
       <c r="D558">
-        <v>4.718794345855713</v>
+        <v>4.703567028045654</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -9394,7 +9394,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D559">
-        <v>2.671257257461548</v>
+        <v>3.774214506149292</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9408,7 +9408,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D560">
-        <v>1.628645300865173</v>
+        <v>2.773436784744263</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -9422,7 +9422,7 @@
         <v>4</v>
       </c>
       <c r="D561">
-        <v>2.531571388244629</v>
+        <v>3.174164533615112</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -9436,7 +9436,7 @@
         <v>2.5</v>
       </c>
       <c r="D562">
-        <v>2.557093381881714</v>
+        <v>3.475639581680298</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -9450,7 +9450,7 @@
         <v>1.5</v>
       </c>
       <c r="D563">
-        <v>3.104216575622559</v>
+        <v>4.029698371887207</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -9464,7 +9464,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D564">
-        <v>2.755103588104248</v>
+        <v>2.828716516494751</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -9478,7 +9478,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D565">
-        <v>1.43027925491333</v>
+        <v>1.88703727722168</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -9492,7 +9492,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D566">
-        <v>2.53124475479126</v>
+        <v>3.292829513549805</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -9506,7 +9506,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D567">
-        <v>5.730343818664551</v>
+        <v>6.411178588867188</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -9520,7 +9520,7 @@
         <v>5.5</v>
       </c>
       <c r="D568">
-        <v>4.603155612945557</v>
+        <v>6.137209415435791</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -9534,7 +9534,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D569">
-        <v>3.757584571838379</v>
+        <v>3.264209985733032</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -9548,7 +9548,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D570">
-        <v>4.55681324005127</v>
+        <v>1.936277389526367</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -9562,7 +9562,7 @@
         <v>4</v>
       </c>
       <c r="D571">
-        <v>1.408604145050049</v>
+        <v>1.770215511322021</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -9576,7 +9576,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D572">
-        <v>1.357839345932007</v>
+        <v>1.627341985702515</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -9590,7 +9590,7 @@
         <v>1.5</v>
       </c>
       <c r="D573">
-        <v>4.213551998138428</v>
+        <v>4.795214653015137</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -9604,7 +9604,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D574">
-        <v>4.329710006713867</v>
+        <v>4.461104393005371</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -9618,7 +9618,7 @@
         <v>0</v>
       </c>
       <c r="D575">
-        <v>1.418822050094604</v>
+        <v>1.863310575485229</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -9632,7 +9632,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D576">
-        <v>3.174672603607178</v>
+        <v>3.306361198425293</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -9646,7 +9646,7 @@
         <v>0.5</v>
       </c>
       <c r="D577">
-        <v>1.37237548828125</v>
+        <v>1.589582800865173</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -9660,7 +9660,7 @@
         <v>0.5</v>
       </c>
       <c r="D578">
-        <v>3.473889827728271</v>
+        <v>2.485840797424316</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -9674,7 +9674,7 @@
         <v>7</v>
       </c>
       <c r="D579">
-        <v>4.667221546173096</v>
+        <v>4.668756484985352</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -9688,7 +9688,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="D580">
-        <v>17.11984252929688</v>
+        <v>19.02688980102539</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -9702,7 +9702,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D581">
-        <v>1.94922947883606</v>
+        <v>2.989912986755371</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -9716,7 +9716,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D582">
-        <v>1.357800602912903</v>
+        <v>1.646323204040527</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -9730,7 +9730,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D583">
-        <v>2.167001724243164</v>
+        <v>2.012512683868408</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -9744,7 +9744,7 @@
         <v>0</v>
       </c>
       <c r="D584">
-        <v>2.342466831207275</v>
+        <v>1.951950550079346</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -9758,7 +9758,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D585">
-        <v>1.517782688140869</v>
+        <v>1.796934723854065</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -9772,7 +9772,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D586">
-        <v>4.811005115509033</v>
+        <v>4.801237106323242</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -9786,7 +9786,7 @@
         <v>2</v>
       </c>
       <c r="D587">
-        <v>4.17606782913208</v>
+        <v>1.880954623222351</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -9800,7 +9800,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D588">
-        <v>2.862860679626465</v>
+        <v>2.33906078338623</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -9814,7 +9814,7 @@
         <v>10</v>
       </c>
       <c r="D589">
-        <v>5.890124320983887</v>
+        <v>6.22008752822876</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -9828,7 +9828,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D590">
-        <v>1.407639741897583</v>
+        <v>1.904486417770386</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -9842,7 +9842,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D591">
-        <v>1.522148609161377</v>
+        <v>1.896083474159241</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -9856,7 +9856,7 @@
         <v>34.59999847412109</v>
       </c>
       <c r="D592">
-        <v>32.57334899902344</v>
+        <v>33.65721893310547</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -9870,7 +9870,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D593">
-        <v>5.000550270080566</v>
+        <v>5.865750312805176</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -9884,7 +9884,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D594">
-        <v>2.605822801589966</v>
+        <v>2.896722793579102</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -9898,7 +9898,7 @@
         <v>0.5</v>
       </c>
       <c r="D595">
-        <v>1.758697390556335</v>
+        <v>1.277238845825195</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -9912,7 +9912,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D596">
-        <v>3.035634756088257</v>
+        <v>3.786412000656128</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -9926,7 +9926,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D597">
-        <v>2.259857892990112</v>
+        <v>2.045202732086182</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -9940,7 +9940,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D598">
-        <v>3.85413670539856</v>
+        <v>3.526508331298828</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -9954,7 +9954,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D599">
-        <v>4.393064975738525</v>
+        <v>3.896496295928955</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -9968,7 +9968,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D600">
-        <v>2.91461968421936</v>
+        <v>2.215970277786255</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -9982,7 +9982,7 @@
         <v>12.19999980926514</v>
       </c>
       <c r="D601">
-        <v>5.391934394836426</v>
+        <v>9.003372192382812</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -9996,7 +9996,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D602">
-        <v>1.401453614234924</v>
+        <v>1.778820037841797</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -10010,7 +10010,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D603">
-        <v>1.393130779266357</v>
+        <v>1.835904002189636</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -10024,7 +10024,7 @@
         <v>1</v>
       </c>
       <c r="D604">
-        <v>1.377587795257568</v>
+        <v>2.555095672607422</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -10038,7 +10038,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D605">
-        <v>6.395354270935059</v>
+        <v>4.06232738494873</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -10052,7 +10052,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D606">
-        <v>1.356616020202637</v>
+        <v>1.198930263519287</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -10066,7 +10066,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D607">
-        <v>1.594496011734009</v>
+        <v>1.88870096206665</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -10080,7 +10080,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D608">
-        <v>6.411478042602539</v>
+        <v>5.74286413192749</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -10094,7 +10094,7 @@
         <v>0.5</v>
       </c>
       <c r="D609">
-        <v>1.374777793884277</v>
+        <v>2.105499267578125</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -10108,7 +10108,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D610">
-        <v>2.675057172775269</v>
+        <v>1.872073769569397</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -10122,7 +10122,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D611">
-        <v>3.670863628387451</v>
+        <v>3.551343202590942</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -10136,7 +10136,7 @@
         <v>3</v>
       </c>
       <c r="D612">
-        <v>1.706292033195496</v>
+        <v>3.272372245788574</v>
       </c>
     </row>
   </sheetData>
